--- a/astro-site/public/dl/kit-tareas-chocolateria/BONUS-01-briefing-servicio.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/BONUS-01-briefing-servicio.xlsx
@@ -647,7 +647,7 @@
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+          <t>Versión 2.1 · octubre 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Temperatura y humedad del obrador al arrancar: ____ °C / ____ % (objetivo 18-20 °C y menos del 60 %)</t>
+          <t>Temperatura y humedad del obrador al arrancar: ____ °C / ____ % (objetivo 18-20 °C y 50-60 %)</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
